--- a/results/qc/cell_lines_sensitivity_QC.xlsx
+++ b/results/qc/cell_lines_sensitivity_QC.xlsx
@@ -551,25 +551,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0322632282735863</v>
+        <v>0.021608</v>
       </c>
       <c r="E2" t="n">
-        <v>0.895179925758843</v>
+        <v>0.907932</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.997302</v>
       </c>
       <c r="G2" t="n">
-        <v>1597</v>
+        <v>1209</v>
       </c>
       <c r="H2" t="n">
-        <v>10.10759493670886</v>
+        <v>8.201058201058201</v>
       </c>
     </row>
     <row r="3">
@@ -579,25 +579,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C3" t="n">
         <v>286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0177231715501543</v>
+        <v>0.025104</v>
       </c>
       <c r="E3" t="n">
-        <v>0.913345536513026</v>
+        <v>0.945522</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.993346</v>
       </c>
       <c r="G3" t="n">
-        <v>2873</v>
+        <v>2096</v>
       </c>
       <c r="H3" t="n">
-        <v>19.69696969696969</v>
+        <v>18.32167832167832</v>
       </c>
     </row>
     <row r="4">

--- a/results/qc/cell_lines_sensitivity_QC.xlsx
+++ b/results/qc/cell_lines_sensitivity_QC.xlsx
@@ -551,25 +551,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>378</v>
+        <v>316</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021608</v>
+        <v>0.0322632282735863</v>
       </c>
       <c r="E2" t="n">
-        <v>0.907932</v>
+        <v>0.895179925758843</v>
       </c>
       <c r="F2" t="n">
-        <v>0.997302</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1209</v>
+        <v>1597</v>
       </c>
       <c r="H2" t="n">
-        <v>8.201058201058201</v>
+        <v>10.10759493670886</v>
       </c>
     </row>
     <row r="3">
@@ -579,25 +579,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C3" t="n">
         <v>286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.025104</v>
+        <v>0.0177231715501543</v>
       </c>
       <c r="E3" t="n">
-        <v>0.945522</v>
+        <v>0.913345536513026</v>
       </c>
       <c r="F3" t="n">
-        <v>0.993346</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2096</v>
+        <v>2873</v>
       </c>
       <c r="H3" t="n">
-        <v>18.32167832167832</v>
+        <v>19.69696969696969</v>
       </c>
     </row>
     <row r="4">
